--- a/public/docs/ImportBrandTemplate.xlsx
+++ b/public/docs/ImportBrandTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahwal\Documents\Template Exel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fauza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DFF835-705B-4C10-B7E2-0685095E55F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2A0529-49C0-4EA2-847C-2F7FB684C248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="405" windowWidth="20400" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import Brand" sheetId="1" r:id="rId1"/>
@@ -58,20 +58,20 @@
     <t>Lenovo</t>
   </si>
   <si>
-    <t>*Wajib Diisi agar master aset bisa mengambil data brand</t>
-  </si>
-  <si>
     <t>*Nama Brand</t>
   </si>
   <si>
     <t>NOTE :BUKA BATAS PENGISIAN</t>
+  </si>
+  <si>
+    <t>*Wajib Diisi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,25 +87,29 @@
       <family val="1"/>
     </font>
     <font>
+      <i/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="18"/>
-      <color theme="0"/>
-      <name val="Georgia"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
@@ -113,18 +117,16 @@
       <i/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -142,13 +144,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -191,41 +193,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -509,10 +512,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="32.44140625" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -520,21 +525,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>12</v>
+      <c r="C2" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -549,51 +554,53 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="71.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="21.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23" style="5" customWidth="1"/>
+    <col min="5" max="5" width="71.33203125" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="9">
+    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11">
         <v>50</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>10</v>
+      <c r="E3" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
